--- a/demo/database/data/dataset_v5.xlsx
+++ b/demo/database/data/dataset_v5.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23715" windowHeight="11340" activeTab="6"/>
+    <workbookView windowWidth="23715" windowHeight="11340" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="2" r:id="rId1"/>
